--- a/assignment/Stack AI Rewire - Data Engineering - Silver Layer - Evaluation Rubric.xlsx
+++ b/assignment/Stack AI Rewire - Data Engineering - Silver Layer - Evaluation Rubric.xlsx
@@ -1,151 +1,220 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chinmaya\Stack_AI_Rewire\assignment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36031251-CCA4-478F-8922-70587F32C2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rubric" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Skill-Driven Evidence Log" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Rubric" sheetId="1" r:id="rId1"/>
+    <sheet name="Skill-Driven Evidence Log" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
-  <si>
-    <t xml:space="preserve">Stack AI Rewire - Data Engineering - Silver Layer - Evaluation Rubric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weighting: 60% AI-Native Engineering / 40% Data Engineering Implementation. Yellow cells are for the evaluator to fill in.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sub-Criterion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Score Earned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Evaluator Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-NATIVE ENGINEERING (60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-Native Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 0: Skill-driven workflow evidence present for every applicable task (2,3,5,6,7,8)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 2: Deduplication skill gap correctly identified and skill modified before implementation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 6: SCD2 skill gap (out-of-order effective_date) correctly identified and skill modified before implementation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 7: Entity resolution SKILL.md authored from scratch, follows required structure, is genuinely reusable</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 8: Pipeline guardrails SKILL.md authored from scratch, covers all 5 required rules</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill quality: no hardcoded assignment-specific literals, no full solution code embedded, single-capability focus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill-driven evidence log: gap found, change made, and validation recorded per task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DATA ENGINEERING IMPLEMENTATION (40%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 1: Batch 1 baseline loaded correctly into silver with consistent types</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 3: Type casting correctness (dates, plan_id casing) and unrecognized-format row quarantined</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 4: Interim testing evidence for Batch 2/Batch 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 5: SCD2 correctness - exactly one is_current row per account, history queryable by date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 9: pytest suite covers transformation logic, bad-record handling, quarantine behavior, expected outputs, and guardrail rules, with a saved pass/fail report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Guardrail correctness in practice: row-count conservation, masked-field integrity, idempotent re-run, non-destructive writes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Code quality: readable, modular, matches the project structure in the Helper Guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill-Driven Evidence Log</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fill in one row per task that involved a skill (Tasks 2, 3, 5, 6, 7, 8). Yellow cells are where you enter your own evidence.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill Used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gap Identified (if any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Change Made (modified / created)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How Validated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Task 2 (example - delete before submitting)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">deduplication/SKILL.md</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No rule for a repeated invoice_id with conflicting non-key values; original skill only covered new-key and identical-key cases.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Added a decision rule: conflicting-key rows are quarantined with reason 'conflicting_key', not inserted or overwritten.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Re-ran Batch 2; confirmed silver invoices count unchanged and exactly 2 rows in quarantine with the correct reason.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="58">
+  <si>
+    <t>Stack AI Rewire - Data Engineering - Silver Layer - Evaluation Rubric</t>
+  </si>
+  <si>
+    <t>Weighting: 60% AI-Native Engineering / 40% Data Engineering Implementation. Yellow cells are for the evaluator to fill in.</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Sub-Criterion</t>
+  </si>
+  <si>
+    <t>Max Points</t>
+  </si>
+  <si>
+    <t>Score Earned</t>
+  </si>
+  <si>
+    <t>Evaluator Notes</t>
+  </si>
+  <si>
+    <t>AI-NATIVE ENGINEERING (60%)</t>
+  </si>
+  <si>
+    <t>AI-Native Engineering</t>
+  </si>
+  <si>
+    <t>Task 0: Skill-driven workflow evidence present for every applicable task (2,3,5,6,7,8)</t>
+  </si>
+  <si>
+    <t>Task 2: Deduplication skill gap correctly identified and skill modified before implementation</t>
+  </si>
+  <si>
+    <t>Task 6: SCD2 skill gap (out-of-order effective_date) correctly identified and skill modified before implementation</t>
+  </si>
+  <si>
+    <t>Task 7: Entity resolution SKILL.md authored from scratch, follows required structure, is genuinely reusable</t>
+  </si>
+  <si>
+    <t>Task 8: Pipeline guardrails SKILL.md authored from scratch, covers all 5 required rules</t>
+  </si>
+  <si>
+    <t>Skill quality: no hardcoded assignment-specific literals, no full solution code embedded, single-capability focus</t>
+  </si>
+  <si>
+    <t>Skill-driven evidence log: gap found, change made, and validation recorded per task</t>
+  </si>
+  <si>
+    <t>DATA ENGINEERING IMPLEMENTATION (40%)</t>
+  </si>
+  <si>
+    <t>Data Engineering</t>
+  </si>
+  <si>
+    <t>Task 1: Batch 1 baseline loaded correctly into silver with consistent types</t>
+  </si>
+  <si>
+    <t>Task 3: Type casting correctness (dates, plan_id casing) and unrecognized-format row quarantined</t>
+  </si>
+  <si>
+    <t>Task 4: Interim testing evidence for Batch 2/Batch 3</t>
+  </si>
+  <si>
+    <t>Task 5: SCD2 correctness - exactly one is_current row per account, history queryable by date</t>
+  </si>
+  <si>
+    <t>Task 9: pytest suite covers transformation logic, bad-record handling, quarantine behavior, expected outputs, and guardrail rules, with a saved pass/fail report</t>
+  </si>
+  <si>
+    <t>Guardrail correctness in practice: row-count conservation, masked-field integrity, idempotent re-run, non-destructive writes</t>
+  </si>
+  <si>
+    <t>Code quality: readable, modular, matches the project structure in the Helper Guide</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Skill-Driven Evidence Log</t>
+  </si>
+  <si>
+    <t>Fill in one row per task that involved a skill (Tasks 2, 3, 5, 6, 7, 8). Yellow cells are where you enter your own evidence.</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Skill Used</t>
+  </si>
+  <si>
+    <t>Gap Identified (if any)</t>
+  </si>
+  <si>
+    <t>Change Made (modified / created)</t>
+  </si>
+  <si>
+    <t>How Validated</t>
+  </si>
+  <si>
+    <t>Task 2</t>
+  </si>
+  <si>
+    <t>deduplication/SKILL.md</t>
+  </si>
+  <si>
+    <t>Starting skill only distinguished new key vs identical row; lacked rules distinguishing mutable column updates (payment_status) from identity-defining column conflicts (account_id, invoice_date, currency).</t>
+  </si>
+  <si>
+    <t>Modified deduplication/SKILL.md to formalize 3 explicit outcomes: retain-unchanged for true duplicate retries, overwrite-as-update in place (no history) for mutable updates, and quarantine with reason conflicting_key for identity-defining conflicts.</t>
+  </si>
+  <si>
+    <t>Validated with test_dedup.py: silver invoice count unchanged (480 rows), 4 retries skipped, 2 conflicting rows quarantined under invoices_quarantine/ with reason conflicting_key.</t>
+  </si>
+  <si>
+    <t>Task 3</t>
+  </si>
+  <si>
+    <t>type_casting/SKILL.md</t>
+  </si>
+  <si>
+    <t>Skill covered standard dual-source date/amount casting (YYYY-MM-DD vs MM/DD/YYYY) but required explicit quarantine routing rather than nulling or crashing on unrecognized textual date formats.</t>
+  </si>
+  <si>
+    <t>Applied type_casting/SKILL.md for MM/DD/YYYY to YYYY-MM-DD parsing and uppercase plan_id normalization; implemented strict format validation that routes unparseable long-form dates to quarantine with unrecognized_format.</t>
+  </si>
+  <si>
+    <t>Validated with test_type_casting.py: 3 valid accounts normalized in silver_billing_accounts, 1 unrecognized textual date quarantined under billing_accounts_quarantine/ with reason unrecognized_format.</t>
+  </si>
+  <si>
+    <t>Task 5 &amp; 6</t>
+  </si>
+  <si>
+    <t>scd2_history/SKILL.md</t>
+  </si>
+  <si>
+    <t>Original skill lacked handling for out-of-order effective dates (e.g., effective_date earlier than existing record valid_from), which would corrupt interval continuity or create overlapping active records.</t>
+  </si>
+  <si>
+    <t>Modified scd2_history/SKILL.md before implementation to add decision rules for out-of-order events: validate effective_date &gt;= valid_from; close prior row (valid_to = effective_date, is_current = false) and append new row; quarantine out-of-order rows with out_of_order_effective_date.</t>
+  </si>
+  <si>
+    <t>Validated with test_scd2.py: exactly one is_current=True row per account at all times, historical plan queries by date return expected tier, and 1 out-of-order plan change safely quarantined.</t>
+  </si>
+  <si>
+    <t>Task 7</t>
+  </si>
+  <si>
+    <t>entity_resolution/SKILL.md</t>
+  </si>
+  <si>
+    <t>No skill existed. Deduplication and SCD2 assume a repeated account_id refers to the same customer entity; when a post-migration system reassigns account IDs to different customers, histories would incorrectly merge and leak data.</t>
+  </si>
+  <si>
+    <t>Authored entity_resolution/SKILL.md from scratch following standard template. Defines attribute continuity checks (customer_name, source_system), assigns surrogate identity (account_id-source_system) on conflict, and enforces email_masked passthrough without unmasking/cross-joins.</t>
+  </si>
+  <si>
+    <t>Validated with test_entity_resolution.py: 3 reused IDs assigned distinct identities, legacy history untouched, and email_masked byte-identical with zero join exposure.</t>
+  </si>
+  <si>
+    <t>Task 8</t>
+  </si>
+  <si>
+    <t>pipeline_guardrails/SKILL.md</t>
+  </si>
+  <si>
+    <t>No skill existed. Individual transformation skills handle localized logic, but lack cross-cutting safety guarantees across the entire multi-batch pipeline.</t>
+  </si>
+  <si>
+    <t>Authored pipeline_guardrails/SKILL.md from scratch covering all 5 core guardrail rules: row-count conservation (input = silver + quarantine + skipped), controlled vocabulary quarantine reasons, masked-field byte immutability, idempotent re-runs, and non-destructive writes.</t>
+  </si>
+  <si>
+    <t>Validated with test_guardrails.py: all 5 programmatic guardrail assertion tests pass; pipeline execution verified idempotent on repeated runs.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -154,45 +223,26 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -222,15 +272,15 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="6">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FF999999"/>
       </left>
@@ -245,82 +295,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -379,47 +450,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -427,12 +514,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -461,7 +548,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -482,7 +569,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -533,7 +620,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -551,40 +638,39 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col min="1" max="1" width="24" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:5" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -601,343 +687,366 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="9"/>
+    </row>
+    <row r="5" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="6">
         <v>10</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="6">
         <v>8</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="6">
         <v>8</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="6">
         <v>10</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="6">
         <v>10</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="6">
         <v>8</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="6">
         <v>6</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-    </row>
-    <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="9"/>
+    </row>
+    <row r="13" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="6">
         <v>3</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="6">
         <v>6</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="6">
         <v>3</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="6">
         <v>6</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" spans="1:5" ht="52.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="6">
         <v>12</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="6">
         <v>6</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="6">
         <v>4</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="8" t="n">
-        <f aca="false">SUM(C5:C19)</f>
+      <c r="B20" s="9"/>
+      <c r="C20" s="4">
+        <f>SUM(C5:C19)</f>
         <v>100</v>
       </c>
-      <c r="D20" s="8" t="n">
-        <f aca="false">SUM(D5:D19)</f>
+      <c r="D20" s="4">
+        <f>SUM(D5:D19)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="8"/>
+      <c r="E20" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A12:E12"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A20:B20"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="30"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+    </row>
+    <row r="3" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="14" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/assignment/Stack AI Rewire - Data Engineering - Silver Layer - Evaluation Rubric.xlsx
+++ b/assignment/Stack AI Rewire - Data Engineering - Silver Layer - Evaluation Rubric.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Chinmaya\Stack_AI_Rewire\assignment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36031251-CCA4-478F-8922-70587F32C2C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0BA6ED-B3BB-4FAF-B1FA-4DBAEA49B32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,7 +272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -347,11 +347,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -368,23 +377,20 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -688,13 +694,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="9"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -788,13 +794,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="9"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="11"/>
     </row>
     <row r="13" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -888,10 +894,10 @@
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="9"/>
+      <c r="B20" s="11"/>
       <c r="C20" s="4">
         <f>SUM(C5:C19)</f>
         <v>100</v>
@@ -918,134 +924,138 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:5" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="2" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-    </row>
-    <row r="3" spans="1:5" ht="26.85" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+    </row>
+    <row r="3" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="8" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:5" ht="135" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:5" ht="150" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="9" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:5" ht="180" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="9" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    <row r="8" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="9" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
